--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N83_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N83_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.64207777756926</v>
+        <v>4.491837638855006</v>
       </c>
       <c r="D2" t="n">
-        <v>27.52972474240187</v>
+        <v>4.473580270640305</v>
       </c>
       <c r="E2" t="n">
-        <v>11.50971804936835</v>
+        <v>1.870329183022357</v>
       </c>
       <c r="F2" t="n">
-        <v>16.67245163933387</v>
+        <v>2.709273391391754</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.10230814280963</v>
+        <v>8.141625073206564</v>
       </c>
       <c r="D3" t="n">
-        <v>51.60974725004898</v>
+        <v>8.386583928132961</v>
       </c>
       <c r="E3" t="n">
-        <v>11.50971804936835</v>
+        <v>1.870329183022357</v>
       </c>
       <c r="F3" t="n">
-        <v>16.67245163933387</v>
+        <v>2.709273391391754</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.99638397670715</v>
+        <v>4.711912396214912</v>
       </c>
       <c r="D4" t="n">
-        <v>4.800389675907207</v>
+        <v>0.7800633223349211</v>
       </c>
       <c r="E4" t="n">
-        <v>11.50971804936835</v>
+        <v>1.870329183022357</v>
       </c>
       <c r="F4" t="n">
-        <v>16.67245163933387</v>
+        <v>2.709273391391754</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.91871758610824</v>
+        <v>2.261791607742589</v>
       </c>
       <c r="D5" t="n">
-        <v>10.17055175807335</v>
+        <v>1.652714660686919</v>
       </c>
       <c r="E5" t="n">
-        <v>11.50971804936835</v>
+        <v>1.870329183022357</v>
       </c>
       <c r="F5" t="n">
-        <v>16.67245163933387</v>
+        <v>2.709273391391754</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.68890042293722</v>
+        <v>6.936946318727299</v>
       </c>
       <c r="D6" t="n">
-        <v>43.12783948968539</v>
+        <v>7.008273917073875</v>
       </c>
       <c r="E6" t="n">
-        <v>11.50971804936835</v>
+        <v>1.870329183022357</v>
       </c>
       <c r="F6" t="n">
-        <v>16.67245163933387</v>
+        <v>2.709273391391754</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>33.14952302880949</v>
+        <v>5.386797492181542</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11284070506861</v>
+        <v>5.380836614573648</v>
       </c>
       <c r="E7" t="n">
-        <v>11.50971804936835</v>
+        <v>1.870329183022357</v>
       </c>
       <c r="F7" t="n">
-        <v>16.67245163933387</v>
+        <v>2.709273391391754</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
